--- a/deliverables/verified_20260910/model_z/timesfm_candidate/official-report.xlsx
+++ b/deliverables/verified_20260910/model_z/timesfm_candidate/official-report.xlsx
@@ -620,14 +620,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источник: /root/projects/TimesOil/results/audit-20260909/timesfm-trained-z-policy-20260909/cycles/candidate-v2/.chdd-8ut47fp0/input.csv  |  Период: 2007–2025  |  Версия ядра: 7.0.2-negative-row-filter</t>
+          <t>Источник: /root/projects/TimesOil/results/audit-20260909/timesfm-early-identity-z-policy-20260910/cycles/candidate/.chdd-sq90py0s/input.csv  |  Период: 2007–2025  |  Версия ядра: 7.0.2-negative-row-filter</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Итоговый ЧДД: 14 128.268 млн руб.   |   ИДДз: 1.254   |   Остановки/запуски: 23 событий   |   Переводы под закачку: 9</t>
+          <t>Итоговый ЧДД: 14 092.343 млн руб.   |   ИДДз: 1.255   |   Остановки/запуски: 23 событий   |   Переводы под закачку: 9</t>
         </is>
       </c>
     </row>
@@ -729,61 +729,61 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1918.362301400732</v>
+        <v>1916.704776942331</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2420.092489589189</v>
+        <v>2415.844065739694</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2951.070803043487</v>
+        <v>2944.993902593317</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>3495.415052844261</v>
+        <v>3489.19903473992</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>4090.200274686315</v>
+        <v>4081.72578011058</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>4751.968115489632</v>
+        <v>4738.121882975597</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>5457.427048210709</v>
+        <v>5435.722995552069</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>6202.234380641301</v>
+        <v>6170.647170560122</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>6996.553736430182</v>
+        <v>6953.696245082027</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>7837.896596817938</v>
+        <v>7782.387897681647</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>8713.798056056463</v>
+        <v>8644.268524005773</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>9627.141637785688</v>
+        <v>9542.786815742866</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>10581.93252418101</v>
+        <v>10482.21802209614</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>11564.75868013038</v>
+        <v>11449.36880131495</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>12568.95152798849</v>
+        <v>12437.24869080448</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>13598.56028944808</v>
+        <v>13449.59612401783</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>14651.76029731474</v>
+        <v>14485.26239779133</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>15730.54645749518</v>
+        <v>15546.14599620645</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>16461.0566849576</v>
+        <v>16264.58081937182</v>
       </c>
     </row>
     <row r="8">
@@ -803,61 +803,61 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1725.415456428887</v>
+        <v>1723.658826069763</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>2148.032782887971</v>
+        <v>2143.764401532144</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2549.58008906343</v>
+        <v>2544.471238370205</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>2883.003063816415</v>
+        <v>2878.904674194498</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>3173.550352220505</v>
+        <v>3169.658369075908</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>3449.997692862526</v>
+        <v>3445.23814367603</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>3705.140147001337</v>
+        <v>3699.84935158007</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>3937.78281689742</v>
+        <v>3931.230530305425</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>4150.945822066882</v>
+        <v>4143.232373546362</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>4350.573109174101</v>
+        <v>4341.620345454676</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>4526.629854340585</v>
+        <v>4516.581152621317</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>4688.091841060597</v>
+        <v>4676.952100690261</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>4843.60830954922</v>
+        <v>4831.444865310174</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>4986.423972378336</v>
+        <v>4973.780994657234</v>
       </c>
       <c r="R8" s="13" t="n">
-        <v>5116.9380492206</v>
+        <v>5104.564712883479</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>5237.822125977357</v>
+        <v>5226.106502767334</v>
       </c>
       <c r="T8" s="13" t="n">
-        <v>5351.615121625777</v>
+        <v>5340.254844740782</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>5459.00037455155</v>
+        <v>5447.797698663208</v>
       </c>
       <c r="V8" s="13" t="n">
-        <v>5527.407043925402</v>
+        <v>5516.254290765401</v>
       </c>
     </row>
     <row r="9">
@@ -877,61 +877,61 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2133.976450194</v>
+        <v>2133.534598146</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2889.106569335</v>
+        <v>2882.841431639</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3682.591795897</v>
+        <v>3669.359730468</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>4494.832205604</v>
+        <v>4480.983111105</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>5357.91911859</v>
+        <v>5336.608551083999</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>6291.656118408</v>
+        <v>6257.215530517</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>7249.041435547</v>
+        <v>7198.976174319</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>8230.062513184001</v>
+        <v>8163.265908201</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>9247.743211915</v>
+        <v>9163.524717774</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>10303.221462402</v>
+        <v>10200.142291992</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>11393.119076172</v>
+        <v>11269.642861328</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>12507.204928771</v>
+        <v>12363.194556427</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>13653.786790041</v>
+        <v>13488.875125488</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>14825.590301759</v>
+        <v>14638.966838866</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>16011.289279295</v>
+        <v>15802.654667969</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>17221.052837892</v>
+        <v>16990.213298828</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>18444.365080078</v>
+        <v>18191.105937502</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>19688.611476563</v>
+        <v>19412.110132813</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>20523.121695311</v>
+        <v>20231.217835938</v>
       </c>
     </row>
     <row r="10">
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>412.3273117429577</v>
+        <v>410.6697872845565</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>501.7301881884569</v>
+        <v>499.1392887973628</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>530.9783134542974</v>
+        <v>529.1498368536231</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>544.3442498007738</v>
+        <v>544.2051321466025</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>594.7852218420541</v>
+        <v>592.5267453706601</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>661.7678408033179</v>
+        <v>656.3961028650167</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>705.4589327210757</v>
+        <v>697.6011125764725</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>744.8073324305932</v>
+        <v>734.9241750080523</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>794.3193557888809</v>
+        <v>783.049074521905</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>841.3428603877567</v>
+        <v>828.6916525996206</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>875.9014592385236</v>
+        <v>861.880626324126</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>913.343581729226</v>
+        <v>898.518291737093</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>954.7908863953172</v>
+        <v>939.4312063532744</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>982.8261559493741</v>
+        <v>967.150779218816</v>
       </c>
       <c r="R10" s="13" t="n">
-        <v>1004.192847858115</v>
+        <v>987.8798894895285</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>1029.608761459585</v>
+        <v>1012.347433213346</v>
       </c>
       <c r="T10" s="13" t="n">
-        <v>1053.200007866661</v>
+        <v>1035.6662737735</v>
       </c>
       <c r="U10" s="13" t="n">
-        <v>1078.78616018044</v>
+        <v>1060.883598415116</v>
       </c>
       <c r="V10" s="13" t="n">
-        <v>730.5102274624235</v>
+        <v>718.4348231653751</v>
       </c>
     </row>
     <row r="11">
@@ -1025,61 +1025,61 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>366.6201229968927</v>
+        <v>364.8634926377685</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>422.6173264590838</v>
+        <v>420.1055754623808</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>401.5473061754585</v>
+        <v>400.7068368380613</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>333.4229747529848</v>
+        <v>334.4334358242924</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>290.5472884040911</v>
+        <v>290.7536948814102</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>276.4473406420206</v>
+        <v>275.5797746001217</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>255.1424541388109</v>
+        <v>254.6112079040404</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>232.6426698960832</v>
+        <v>231.3811787253553</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>213.1630051694618</v>
+        <v>212.001843240937</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>199.6272871072187</v>
+        <v>198.3879719083139</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>176.0567451664845</v>
+        <v>174.9608071666418</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>161.461986720012</v>
+        <v>160.3709480689429</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>155.5164684886232</v>
+        <v>154.4927646199133</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>142.8156628291152</v>
+        <v>142.3361293470603</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>130.5140768422646</v>
+        <v>130.7837182262444</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>120.8840767567569</v>
+        <v>121.5417898838547</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>113.7929956484196</v>
+        <v>114.1483419734488</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>107.3852529257725</v>
+        <v>107.5428539224265</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>68.40666937385272</v>
+        <v>68.45659210219235</v>
       </c>
     </row>
     <row r="12">
@@ -1099,61 +1099,61 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>649.488776365</v>
+        <v>649.0469243169999</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>755.130119141</v>
+        <v>749.306833493</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>793.485226562</v>
+        <v>786.5182988289999</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>812.240409707</v>
+        <v>811.623380637</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>863.086912986</v>
+        <v>855.625439979</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>933.736999818</v>
+        <v>920.6069794330001</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>957.385317139</v>
+        <v>941.760643802</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>981.021077637</v>
+        <v>964.289733882</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1017.680698731</v>
+        <v>1000.258809573</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1055.478250487</v>
+        <v>1036.617574218</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1089.89761377</v>
+        <v>1069.500569336</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1114.085852599</v>
+        <v>1093.551695099</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1146.58186127</v>
+        <v>1125.680569061</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1171.803511718</v>
+        <v>1150.091713378</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1185.698977536</v>
+        <v>1163.687829103</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1209.763558597</v>
+        <v>1187.558630859</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1223.312242186</v>
+        <v>1200.892638674</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1244.246396485</v>
+        <v>1221.004195311</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>834.5102187479999</v>
+        <v>819.1077031249999</v>
       </c>
     </row>
     <row r="13">
@@ -1321,61 +1321,61 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>21.83390455572289</v>
+        <v>21.72518667168675</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>25.59871135346097</v>
+        <v>25.46401299852724</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>25.97752272701149</v>
+        <v>25.89462594109196</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>25.8096936037464</v>
+        <v>25.81569164553314</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27.43399329624278</v>
+        <v>27.34528639017341</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>30.98103546556886</v>
+        <v>30.745882001497</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>32.69417099550225</v>
+        <v>32.35782376911544</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>33.67932109792284</v>
+        <v>33.24968377596439</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>34.14118179344729</v>
+        <v>33.67772591025641</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>34.83033944937586</v>
+        <v>34.32583446601942</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>35.46536169945355</v>
+        <v>34.91627085928962</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>36.49228142740841</v>
+        <v>35.91629416824966</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>37.05257640608465</v>
+        <v>36.47183367328043</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>37.85621777910053</v>
+        <v>37.27114783333334</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>38.6227708994709</v>
+        <v>38.02030563227513</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>40.10072318951613</v>
+        <v>39.45703117069893</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>40.91510570698924</v>
+        <v>40.25777451612903</v>
       </c>
       <c r="U15" s="9" t="n">
-        <v>41.6979059139785</v>
+        <v>41.02647271370968</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>42.45679489717742</v>
+        <v>41.77372545766129</v>
       </c>
     </row>
     <row r="16">
@@ -1395,61 +1395,61 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>18.17732949560341</v>
+        <v>18.0766183966176</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>20.40976894607839</v>
+        <v>20.28981334970286</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>18.97400671151362</v>
+        <v>18.93449064916099</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>15.79745271438363</v>
+        <v>15.84948174928</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>13.80720380302275</v>
+        <v>13.81726939046806</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>13.56960612190213</v>
+        <v>13.52701907118703</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>12.57813480388729</v>
+        <v>12.55204162019513</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>11.32618374511385</v>
+        <v>11.26333368555634</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>9.985842481575501</v>
+        <v>9.931422711899961</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>9.081536302805741</v>
+        <v>9.025136631762917</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>7.909407772400335</v>
+        <v>7.860178905455554</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>7.20313558092507</v>
+        <v>7.154475661493382</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>6.764567160987148</v>
+        <v>6.720003189025398</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>6.194373256522785</v>
+        <v>6.173536692090638</v>
       </c>
       <c r="R16" s="13" t="n">
-        <v>5.676848695036396</v>
+        <v>5.688493565272909</v>
       </c>
       <c r="S16" s="13" t="n">
-        <v>5.342476302785606</v>
+        <v>5.371561006486002</v>
       </c>
       <c r="T16" s="13" t="n">
-        <v>5.029091643007812</v>
+        <v>5.044814923534238</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>4.732635923964997</v>
+        <v>4.73958558990235</v>
       </c>
       <c r="V16" s="13" t="n">
-        <v>4.540500812348844</v>
+        <v>4.543817067108507</v>
       </c>
     </row>
     <row r="17">
@@ -1469,61 +1469,61 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>64.32049124698796</v>
+        <v>64.2786640120482</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>71.15155682471264</v>
+        <v>70.60189779310345</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>74.95988660919541</v>
+        <v>74.30415711494253</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>75.6572454532578</v>
+        <v>75.58674261756374</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>74.86018271503957</v>
+        <v>74.21412234036939</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>70.21426212155964</v>
+        <v>69.22711755504587</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>69.02255232456139</v>
+        <v>67.89630500438595</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>70.73822729166668</v>
+        <v>69.53212152631578</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>73.36786542105264</v>
+        <v>72.11189715789473</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>74.25812358798284</v>
+        <v>72.93125120171675</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>76.55639584829061</v>
+        <v>75.12397761965813</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>77.92722451914894</v>
+        <v>76.49079737021277</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>78.52884100833333</v>
+        <v>77.09727581041668</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>80.03975649166667</v>
+        <v>78.55680362291668</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>81.20963689583336</v>
+        <v>79.70212404791667</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>80.83797573170732</v>
+        <v>79.35413085365855</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>81.74273753455284</v>
+        <v>80.2444778191057</v>
       </c>
       <c r="U17" s="9" t="n">
-        <v>82.91563351016261</v>
+        <v>81.36677822560975</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>83.75730001829268</v>
+        <v>82.21135821951219</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1568,13 +1568,13 @@
         <v>7</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" s="16" t="n">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>0</v>
       </c>
       <c r="Q19" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" s="16" t="n">
         <v>5</v>
@@ -1642,13 +1642,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>1</v>
@@ -1663,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="14" t="n">
         <v>5</v>
@@ -2086,13 +2086,13 @@
         <v>12.6</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>1.8</v>
@@ -2107,16 +2107,16 @@
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="R26" s="13" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="S26" s="13" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="T26" s="13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U26" s="13" t="n">
         <v>9</v>
@@ -2388,13 +2388,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="14" t="n">
         <v>0</v>
@@ -2456,10 +2456,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="16" t="n">
         <v>1</v>
@@ -2486,10 +2486,10 @@
         <v>1</v>
       </c>
       <c r="T31" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V31" s="16" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="14" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32" s="14" t="n">
         <v>1</v>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V32" s="14" t="n">
         <v>2</v>
@@ -2628,10 +2628,10 @@
         <v>0</v>
       </c>
       <c r="R33" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" s="16" t="n">
         <v>0</v>
@@ -3858,61 +3858,61 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>10265.36344391299</v>
+        <v>10216.17779385752</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>11833.28514085435</v>
+        <v>11762.95611294666</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>11243.32457291284</v>
+        <v>11219.79143146572</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>9335.843293083575</v>
+        <v>9364.136203080188</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>8135.32407531455</v>
+        <v>8141.103456679484</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>7740.525537976578</v>
+        <v>7716.233688803408</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>7143.988715886705</v>
+        <v>7129.113821313131</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>6513.99475709033</v>
+        <v>6478.673004309949</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>5968.564144744931</v>
+        <v>5936.051610746236</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>5589.564039002124</v>
+        <v>5554.863213432789</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>4929.588864661567</v>
+        <v>4898.902600665971</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>4520.935628160337</v>
+        <v>4490.386545930402</v>
       </c>
       <c r="P52" s="13" t="n">
-        <v>4354.461117681451</v>
+        <v>4325.797409357572</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>3998.838559215224</v>
+        <v>3985.411621717688</v>
       </c>
       <c r="R52" s="13" t="n">
-        <v>3654.394151583408</v>
+        <v>3661.944110334843</v>
       </c>
       <c r="S52" s="13" t="n">
-        <v>3384.754149189194</v>
+        <v>3403.170116747933</v>
       </c>
       <c r="T52" s="13" t="n">
-        <v>3186.203878155748</v>
+        <v>3196.153575256566</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>3006.787081921631</v>
+        <v>3011.199909827941</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>1915.386742467876</v>
+        <v>1916.784578861385</v>
       </c>
     </row>
     <row r="53">
@@ -3932,61 +3932,61 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>14.66480491987571</v>
+        <v>14.59453970551074</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>16.90469305836335</v>
+        <v>16.80422301849523</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>16.06189224701834</v>
+        <v>16.02827347352245</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>13.33691899011939</v>
+        <v>13.3773374329717</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>11.62189153616364</v>
+        <v>11.63014779525641</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>11.05789362568082</v>
+        <v>11.02319098400487</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>10.20569816555244</v>
+        <v>10.18444831616162</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>9.305706795843328</v>
+        <v>9.255247149014211</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>8.526520206778473</v>
+        <v>8.48007372963748</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>7.985091484288748</v>
+        <v>7.935518876332556</v>
       </c>
       <c r="N53" s="9" t="n">
-        <v>7.042269806659381</v>
+        <v>6.998432286665672</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>6.458479468800481</v>
+        <v>6.414837922757718</v>
       </c>
       <c r="P53" s="9" t="n">
-        <v>6.22065873954493</v>
+        <v>6.179710584796531</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>5.712626513164606</v>
+        <v>5.693445173882412</v>
       </c>
       <c r="R53" s="9" t="n">
-        <v>5.220563073690583</v>
+        <v>5.231348729049776</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>4.835363070270277</v>
+        <v>4.861671595354189</v>
       </c>
       <c r="T53" s="9" t="n">
-        <v>4.551719825936784</v>
+        <v>4.565933678937951</v>
       </c>
       <c r="U53" s="9" t="n">
-        <v>4.295410117030902</v>
+        <v>4.301714156897058</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2.736266774954109</v>
+        <v>2.738263684087693</v>
       </c>
     </row>
     <row r="54">
@@ -4006,61 +4006,61 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>41.23273117429577</v>
+        <v>41.06697872845565</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>50.17301881884569</v>
+        <v>49.91392887973628</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>53.09783134542975</v>
+        <v>52.91498368536232</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>54.43442498007737</v>
+        <v>54.42051321466025</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>59.4785221842054</v>
+        <v>59.25267453706601</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>66.17678408033179</v>
+        <v>65.63961028650166</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>70.54589327210758</v>
+        <v>69.76011125764724</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>74.48073324305932</v>
+        <v>73.49241750080523</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>79.43193557888807</v>
+        <v>78.30490745219051</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>84.13428603877567</v>
+        <v>82.86916525996207</v>
       </c>
       <c r="N54" s="13" t="n">
-        <v>87.59014592385235</v>
+        <v>86.1880626324126</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>91.33435817292261</v>
+        <v>89.85182917370931</v>
       </c>
       <c r="P54" s="13" t="n">
-        <v>95.47908863953172</v>
+        <v>93.94312063532743</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>98.2826155949374</v>
+        <v>96.7150779218816</v>
       </c>
       <c r="R54" s="13" t="n">
-        <v>100.4192847858115</v>
+        <v>98.78798894895284</v>
       </c>
       <c r="S54" s="13" t="n">
-        <v>102.9608761459585</v>
+        <v>101.2347433213346</v>
       </c>
       <c r="T54" s="13" t="n">
-        <v>105.320000786666</v>
+        <v>103.56662737735</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>107.878616018044</v>
+        <v>106.0883598415116</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>73.05102274624235</v>
+        <v>71.8434823165375</v>
       </c>
     </row>
     <row r="55">
@@ -4080,61 +4080,61 @@
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>19.48466329095</v>
+        <v>19.47140772951</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>22.65390357423</v>
+        <v>22.47920500479</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>23.80455679686</v>
+        <v>23.59554896487</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>24.36721229121</v>
+        <v>24.34870141911</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>25.89260738958</v>
+        <v>25.66876319937</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>28.01210999454</v>
+        <v>27.61820938299</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>28.72155951417</v>
+        <v>28.25281931406</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>29.43063232911</v>
+        <v>28.92869201646</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>30.53042096193</v>
+        <v>30.00776428719</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>31.66434751461</v>
+        <v>31.09852722654</v>
       </c>
       <c r="N55" s="9" t="n">
-        <v>32.6969284131</v>
+        <v>32.08501708008</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>33.42257557797</v>
+        <v>32.80655085297</v>
       </c>
       <c r="P55" s="9" t="n">
-        <v>34.3974558381</v>
+        <v>33.77041707183</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>35.15410535154</v>
+        <v>34.50275140134</v>
       </c>
       <c r="R55" s="9" t="n">
-        <v>35.57096932608</v>
+        <v>34.91063487309</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>36.29290675791</v>
+        <v>35.62675892577</v>
       </c>
       <c r="T55" s="9" t="n">
-        <v>36.69936726558</v>
+        <v>36.02677916022</v>
       </c>
       <c r="U55" s="9" t="n">
-        <v>37.32739189455</v>
+        <v>36.63012585933</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>25.03530656244</v>
+        <v>24.57323109375</v>
       </c>
     </row>
     <row r="56">
@@ -4302,61 +4302,61 @@
         </is>
       </c>
       <c r="D58" s="13" t="n">
-        <v>216.3821993851215</v>
+        <v>216.1329261634764</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>207.7149487847724</v>
+        <v>207.1806902363548</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>183.5642803893081</v>
+        <v>183.1388061237548</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>191.7885562614068</v>
+        <v>191.796552066742</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>204.0430211099491</v>
+        <v>203.6015855316924</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>220.8467877005526</v>
+        <v>219.8810106534965</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>224.4564842851634</v>
+        <v>221.3807122212022</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>216.5837390346793</v>
+        <v>216.8430233329461</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>219.5888767475965</v>
+        <v>216.092745469018</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>227.5003917043411</v>
+        <v>225.6198780295013</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>230.9293441436117</v>
+        <v>228.8715119991583</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>234.7987465530264</v>
+        <v>232.6565512827704</v>
       </c>
       <c r="P58" s="13" t="n">
-        <v>239.0972032171767</v>
+        <v>236.893248291954</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>247.549347459642</v>
+        <v>243.511274497104</v>
       </c>
       <c r="R58" s="13" t="n">
-        <v>247.810817185582</v>
+        <v>243.7299725510926</v>
       </c>
       <c r="S58" s="13" t="n">
-        <v>261.0891459741388</v>
+        <v>260.5231738424587</v>
       </c>
       <c r="T58" s="13" t="n">
-        <v>251.3710878781828</v>
+        <v>247.159340216508</v>
       </c>
       <c r="U58" s="13" t="n">
-        <v>261.5014180296249</v>
+        <v>259.0201998577387</v>
       </c>
       <c r="V58" s="13" t="n">
-        <v>173.0892627503031</v>
+        <v>171.4216437610418</v>
       </c>
     </row>
     <row r="59">
@@ -4394,19 +4394,19 @@
         <v>5.15794</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>5.95397</v>
+        <v>5.20397</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>3.46191</v>
+        <v>4.21191</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="M59" s="9" t="n">
         <v>0.65</v>
       </c>
       <c r="N59" s="9" t="n">
-        <v>1.80794</v>
+        <v>1.55397</v>
       </c>
       <c r="O59" s="9" t="n">
         <v>0</v>
@@ -4415,19 +4415,19 @@
         <v>0</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>2.55794</v>
+        <v>1.65397</v>
       </c>
       <c r="R59" s="9" t="n">
-        <v>2.75397</v>
+        <v>0.9039700000000001</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>5.05794</v>
+        <v>6.90794</v>
       </c>
       <c r="T59" s="9" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="U59" s="9" t="n">
-        <v>4.05794</v>
+        <v>4.21191</v>
       </c>
       <c r="V59" s="9" t="n">
         <v>1.80794</v>
@@ -4524,61 +4524,61 @@
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>7185.754410739097</v>
+        <v>7151.324455700263</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>8283.299598598043</v>
+        <v>8234.069279062664</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>7870.327201038986</v>
+        <v>7853.854002026002</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>6535.090305158502</v>
+        <v>6554.895342156132</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>5694.726852720185</v>
+        <v>5698.772419675639</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>5418.367876583604</v>
+        <v>5401.363582162385</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>5000.792101120694</v>
+        <v>4990.379674919192</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>4559.796329963231</v>
+        <v>4535.071103016964</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>4177.994901321452</v>
+        <v>4155.236127522366</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>3912.694827301487</v>
+        <v>3888.404249402952</v>
       </c>
       <c r="N61" s="9" t="n">
-        <v>3450.712205263097</v>
+        <v>3429.231820466179</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>3164.654939712235</v>
+        <v>3143.270582151281</v>
       </c>
       <c r="P61" s="9" t="n">
-        <v>3048.122782377015</v>
+        <v>3028.0581865503</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>2799.186991450656</v>
+        <v>2789.788135202382</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>2558.075906108385</v>
+        <v>2563.360877234391</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>2369.327904432435</v>
+        <v>2382.219081723553</v>
       </c>
       <c r="T61" s="9" t="n">
-        <v>2230.342714709024</v>
+        <v>2237.307502679596</v>
       </c>
       <c r="U61" s="9" t="n">
-        <v>2104.750957345142</v>
+        <v>2107.839936879559</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>1340.770719727513</v>
+        <v>1341.74920520297</v>
       </c>
     </row>
     <row r="62">
@@ -4598,61 +4598,61 @@
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>2863.226833788777</v>
+        <v>2848.720411993779</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>3342.270593471532</v>
+        <v>3321.706143647644</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3189.433091484542</v>
+        <v>3182.79862331596</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>2608.964431663666</v>
+        <v>2617.444308857315</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>2236.554201484416</v>
+        <v>2238.729451472153</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2101.310873692421</v>
+        <v>2094.989095987526</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>1918.740130480848</v>
+        <v>1917.353434172737</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>1737.61468809242</v>
+        <v>1726.758877960038</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>1570.980366675883</v>
+        <v>1564.722737754853</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>1449.368819996296</v>
+        <v>1440.839086000336</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>1247.947315254858</v>
+        <v>1240.799268200633</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>1121.481941895075</v>
+        <v>1114.45941249635</v>
       </c>
       <c r="P62" s="13" t="n">
-        <v>1067.241132087258</v>
+        <v>1060.845974515317</v>
       </c>
       <c r="Q62" s="13" t="n">
-        <v>952.1022203049251</v>
+        <v>952.1122120182025</v>
       </c>
       <c r="R62" s="13" t="n">
-        <v>848.5074282894402</v>
+        <v>854.8532605493604</v>
       </c>
       <c r="S62" s="13" t="n">
-        <v>754.3370987826193</v>
+        <v>760.427861181921</v>
       </c>
       <c r="T62" s="13" t="n">
-        <v>704.4900755685417</v>
+        <v>711.686732360462</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>640.5347065468648</v>
+        <v>644.3397730906435</v>
       </c>
       <c r="V62" s="13" t="n">
-        <v>401.5267599900598</v>
+        <v>403.6137298973738</v>
       </c>
     </row>
     <row r="63">
@@ -4672,61 +4672,61 @@
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>715.8067084471943</v>
+        <v>712.1801029984447</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>835.5676483678831</v>
+        <v>830.4265359119111</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>797.3582728711356</v>
+        <v>795.6996558289901</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>652.2411079159166</v>
+        <v>654.3610772143287</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>559.138550371104</v>
+        <v>559.6823628680382</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>525.3277184231051</v>
+        <v>523.7472739968814</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>479.6850326202121</v>
+        <v>479.3383585431843</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>434.4036720231049</v>
+        <v>431.6897194900096</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>392.7450916689707</v>
+        <v>391.1806844387132</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>362.342204999074</v>
+        <v>360.2097715000839</v>
       </c>
       <c r="N63" s="9" t="n">
-        <v>311.9868288137146</v>
+        <v>310.1998170501582</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>280.3704854737687</v>
+        <v>278.6148531240876</v>
       </c>
       <c r="P63" s="9" t="n">
-        <v>266.8102830218146</v>
+        <v>265.2114936288293</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>238.0255550762313</v>
+        <v>238.0280530045506</v>
       </c>
       <c r="R63" s="9" t="n">
-        <v>212.1268570723601</v>
+        <v>213.7133151373401</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>188.5842746956548</v>
+        <v>190.1069652954803</v>
       </c>
       <c r="T63" s="9" t="n">
-        <v>176.1225188921354</v>
+        <v>177.9216830901155</v>
       </c>
       <c r="U63" s="9" t="n">
-        <v>160.1336766367162</v>
+        <v>161.0849432726609</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>100.3816899975149</v>
+        <v>100.9034324743434</v>
       </c>
     </row>
     <row r="64">
@@ -4746,61 +4746,61 @@
         </is>
       </c>
       <c r="D64" s="13" t="n">
-        <v>2863.226833788777</v>
+        <v>2848.720411993779</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>3342.270593471532</v>
+        <v>3321.706143647644</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>3189.433091484542</v>
+        <v>3182.79862331596</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>2608.964431663666</v>
+        <v>2617.444308857315</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>2236.554201484416</v>
+        <v>2238.729451472153</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>2101.310873692421</v>
+        <v>2094.989095987526</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>1918.740130480848</v>
+        <v>1917.353434172737</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>1737.61468809242</v>
+        <v>1726.758877960038</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>1570.980366675883</v>
+        <v>1564.722737754853</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>1449.368819996296</v>
+        <v>1440.839086000336</v>
       </c>
       <c r="N64" s="13" t="n">
-        <v>1247.947315254858</v>
+        <v>1240.799268200633</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>1121.481941895075</v>
+        <v>1114.45941249635</v>
       </c>
       <c r="P64" s="13" t="n">
-        <v>1067.241132087258</v>
+        <v>1060.845974515317</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>952.1022203049251</v>
+        <v>952.1122120182025</v>
       </c>
       <c r="R64" s="13" t="n">
-        <v>848.5074282894402</v>
+        <v>854.8532605493604</v>
       </c>
       <c r="S64" s="13" t="n">
-        <v>754.3370987826193</v>
+        <v>760.427861181921</v>
       </c>
       <c r="T64" s="13" t="n">
-        <v>704.4900755685417</v>
+        <v>711.686732360462</v>
       </c>
       <c r="U64" s="13" t="n">
-        <v>640.5347065468648</v>
+        <v>644.3397730906435</v>
       </c>
       <c r="V64" s="13" t="n">
-        <v>401.5267599900598</v>
+        <v>403.6137298973738</v>
       </c>
     </row>
     <row r="65">
@@ -4820,61 +4820,61 @@
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2129.662185341583</v>
+        <v>2118.782368995334</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>2497.598975103649</v>
+        <v>2482.175637735733</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2390.674818613407</v>
+        <v>2385.69896748697</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>1954.57332374775</v>
+        <v>1960.933231642986</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>1673.015651113312</v>
+        <v>1674.647088604115</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1570.825215269315</v>
+        <v>1566.083881990644</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1433.101127860636</v>
+        <v>1432.811105629553</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1299.749106069315</v>
+        <v>1290.857248470029</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>1176.835275006912</v>
+        <v>1172.79205331614</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>1086.376614997222</v>
+        <v>1079.979314500252</v>
       </c>
       <c r="N65" s="9" t="n">
-        <v>934.1525464411437</v>
+        <v>929.0454811504746</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>841.1114564213061</v>
+        <v>835.8445593722628</v>
       </c>
       <c r="P65" s="9" t="n">
-        <v>800.4308490654438</v>
+        <v>795.6344808864879</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>711.5187252286938</v>
+        <v>712.4301890136519</v>
       </c>
       <c r="R65" s="9" t="n">
-        <v>633.6266012170801</v>
+        <v>640.2359754120203</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>560.6948840869645</v>
+        <v>563.4129558864407</v>
       </c>
       <c r="T65" s="9" t="n">
-        <v>527.6175566764063</v>
+        <v>533.7650492703465</v>
       </c>
       <c r="U65" s="9" t="n">
-        <v>476.3430899101485</v>
+        <v>479.0429198179826</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>299.3371299925448</v>
+        <v>300.9023574230303</v>
       </c>
     </row>
     <row r="66">
@@ -4968,61 +4968,61 @@
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2129.662185341583</v>
+        <v>2118.782368995334</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2270.544522821499</v>
+        <v>2256.523307032484</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>1975.764312903642</v>
+        <v>1971.65203924543</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>1468.499867579075</v>
+        <v>1473.278160513137</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>1142.692200746746</v>
+        <v>1143.806494504552</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>975.3588709597052</v>
+        <v>972.4148760272483</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>808.948225807994</v>
+        <v>808.7845158194115</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>666.9768054425725</v>
+        <v>662.4138765293475</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>549.0023410818753</v>
+        <v>547.1161483233059</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>460.7297350758835</v>
+        <v>458.0166551711052</v>
       </c>
       <c r="N67" s="9" t="n">
-        <v>360.1562455838917</v>
+        <v>358.1872508323957</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>294.8044342595767</v>
+        <v>292.9584189746904</v>
       </c>
       <c r="P67" s="9" t="n">
-        <v>255.0419359583173</v>
+        <v>253.5136652434167</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>206.1016302144083</v>
+        <v>206.3656488063307</v>
       </c>
       <c r="R67" s="9" t="n">
-        <v>166.8536876601919</v>
+        <v>168.5941424571237</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>134.2258973723839</v>
+        <v>134.8765821507931</v>
       </c>
       <c r="T67" s="9" t="n">
-        <v>114.824952887196</v>
+        <v>116.1628263876915</v>
       </c>
       <c r="U67" s="9" t="n">
-        <v>94.24194090614056</v>
+        <v>94.77608786034267</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>53.83841397535608</v>
+        <v>54.1199338869359</v>
       </c>
     </row>
     <row r="68">
@@ -5042,61 +5042,61 @@
         </is>
       </c>
       <c r="D68" s="13" t="n">
-        <v>2129.662185341583</v>
+        <v>2118.782368995334</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>4400.206708163081</v>
+        <v>4375.305676027819</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>6375.971021066724</v>
+        <v>6346.957715273248</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>7844.470888645799</v>
+        <v>7820.235875786386</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>8987.163089392547</v>
+        <v>8964.042370290937</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>9962.521960352253</v>
+        <v>9936.457246318187</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>10771.47018616025</v>
+        <v>10745.2417621376</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>11438.44699160282</v>
+        <v>11407.65563866695</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>11987.4493326847</v>
+        <v>11954.77178699025</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>12448.17906776058</v>
+        <v>12412.78844216136</v>
       </c>
       <c r="N68" s="13" t="n">
-        <v>12808.33531334447</v>
+        <v>12770.97569299375</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>13103.13974760405</v>
+        <v>13063.93411196844</v>
       </c>
       <c r="P68" s="13" t="n">
-        <v>13358.18168356236</v>
+        <v>13317.44777721186</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>13564.28331377677</v>
+        <v>13523.81342601819</v>
       </c>
       <c r="R68" s="13" t="n">
-        <v>13731.13700143697</v>
+        <v>13692.40756847532</v>
       </c>
       <c r="S68" s="13" t="n">
-        <v>13865.36289880935</v>
+        <v>13827.28415062611</v>
       </c>
       <c r="T68" s="13" t="n">
-        <v>13980.18785169655</v>
+        <v>13943.4469770138</v>
       </c>
       <c r="U68" s="13" t="n">
-        <v>14074.42979260269</v>
+        <v>14038.22306487414</v>
       </c>
       <c r="V68" s="13" t="n">
-        <v>14128.26820657804</v>
+        <v>14092.34299876108</v>
       </c>
     </row>
     <row r="69">
@@ -5116,61 +5116,61 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>10265.36344391299</v>
+        <v>10216.17779385752</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>10757.53194623122</v>
+        <v>10693.59646631515</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>9292.003779266806</v>
+        <v>9272.554902037782</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>7014.157244991415</v>
+        <v>7035.414127032446</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>5556.535807195238</v>
+        <v>5560.483202431175</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>4806.257358213594</v>
+        <v>4791.174031085436</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>4032.595386716406</v>
+        <v>4024.198896517325</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3342.709291713162</v>
+        <v>3324.583647523771</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>2784.379222778704</v>
+        <v>2769.211885718993</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>2370.520796681286</v>
+        <v>2355.804259201772</v>
       </c>
       <c r="N69" s="9" t="n">
-        <v>1900.56990641681</v>
+        <v>1888.739023255644</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>1584.560357618274</v>
+        <v>1573.853090661926</v>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1387.465506614793</v>
+        <v>1378.332365792945</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>1158.321090922228</v>
+        <v>1154.431785400241</v>
       </c>
       <c r="R69" s="9" t="n">
-        <v>962.3161956652608</v>
+        <v>964.3043357732355</v>
       </c>
       <c r="S69" s="9" t="n">
-        <v>810.2832323851799</v>
+        <v>814.6918686001824</v>
       </c>
       <c r="T69" s="9" t="n">
-        <v>693.4107964542552</v>
+        <v>695.5761404356799</v>
       </c>
       <c r="U69" s="9" t="n">
-        <v>594.8767946759882</v>
+        <v>595.7498491520253</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>344.4991417084227</v>
+        <v>344.7505548706504</v>
       </c>
     </row>
     <row r="70">
@@ -5190,61 +5190,61 @@
         </is>
       </c>
       <c r="D70" s="13" t="n">
-        <v>8135.701258571412</v>
+        <v>8097.395424862184</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>8486.987423409724</v>
+        <v>8437.073159282663</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>7316.239466363165</v>
+        <v>7300.902862792351</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>5545.657377412339</v>
+        <v>5562.135966519309</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>4413.843606448491</v>
+        <v>4416.676707926623</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>3830.898487253889</v>
+        <v>3818.759155058187</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>3223.647160908411</v>
+        <v>3215.414380697914</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>2675.732486270589</v>
+        <v>2662.169770994423</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>2235.376881696829</v>
+        <v>2222.095737395687</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>1909.791061605403</v>
+        <v>1897.787604030667</v>
       </c>
       <c r="N70" s="13" t="n">
-        <v>1540.413660832918</v>
+        <v>1530.551772423249</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>1289.755923358697</v>
+        <v>1280.894671687236</v>
       </c>
       <c r="P70" s="13" t="n">
-        <v>1132.423570656476</v>
+        <v>1124.818700549528</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>952.2194607078193</v>
+        <v>948.0661365939102</v>
       </c>
       <c r="R70" s="13" t="n">
-        <v>795.4625080050689</v>
+        <v>795.7101933161118</v>
       </c>
       <c r="S70" s="13" t="n">
-        <v>676.057335012796</v>
+        <v>679.8152864493893</v>
       </c>
       <c r="T70" s="13" t="n">
-        <v>578.5858435670592</v>
+        <v>579.4133140479884</v>
       </c>
       <c r="U70" s="13" t="n">
-        <v>500.6348537698476</v>
+        <v>500.9737612916826</v>
       </c>
       <c r="V70" s="13" t="n">
-        <v>290.6607277330667</v>
+        <v>290.6306209837144</v>
       </c>
     </row>
     <row r="71">
@@ -5264,61 +5264,61 @@
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>1.261767500754513</v>
+        <v>1.261662208379974</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>1.264710889576659</v>
+        <v>1.26461725417794</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>1.266343212258971</v>
+        <v>1.266283146851853</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>1.266053286785841</v>
+        <v>1.266016970956072</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>1.265120340955691</v>
+        <v>1.265097106531171</v>
       </c>
       <c r="I71" s="22" t="n">
-        <v>1.264052464990499</v>
+        <v>1.264036144431428</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>1.263020458072414</v>
+        <v>1.263051989808937</v>
       </c>
       <c r="K71" s="22" t="n">
-        <v>1.262177078080642</v>
+        <v>1.262181506705681</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>1.26136898959793</v>
+        <v>1.26140577468561</v>
       </c>
       <c r="M71" s="22" t="n">
-        <v>1.260564566157918</v>
+        <v>1.260606369787897</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>1.259728683240438</v>
+        <v>1.259778796684207</v>
       </c>
       <c r="O71" s="22" t="n">
-        <v>1.25893463261505</v>
+        <v>1.258989950679848</v>
       </c>
       <c r="P71" s="22" t="n">
-        <v>1.258196628138111</v>
+        <v>1.258256859514566</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>1.257442040665378</v>
+        <v>1.257524133184019</v>
       </c>
       <c r="R71" s="22" t="n">
-        <v>1.256732824880198</v>
+        <v>1.256842832729542</v>
       </c>
       <c r="S71" s="22" t="n">
-        <v>1.256006457428522</v>
+        <v>1.25610697599886</v>
       </c>
       <c r="T71" s="22" t="n">
-        <v>1.255398172935819</v>
+        <v>1.255516373949741</v>
       </c>
       <c r="U71" s="22" t="n">
-        <v>1.254789562617985</v>
+        <v>1.254912950741742</v>
       </c>
       <c r="V71" s="22" t="n">
-        <v>1.254425455409731</v>
+        <v>1.254552309271767</v>
       </c>
     </row>
     <row r="72">
@@ -5344,58 +5344,58 @@
         <v>2.664535259100376e-13</v>
       </c>
       <c r="E73" s="24" t="n">
-        <v>-1.172395514004165e-13</v>
+        <v>-3.446132268436486e-13</v>
       </c>
       <c r="F73" s="24" t="n">
-        <v>1.363353874239692e-13</v>
+        <v>-2.047251257408789e-13</v>
       </c>
       <c r="G73" s="24" t="n">
-        <v>2.264854970235319e-14</v>
+        <v>-2.047251257408789e-13</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>1.367794766338193e-13</v>
+        <v>2.309263891220326e-14</v>
       </c>
       <c r="I73" s="24" t="n">
-        <v>-5.329070518200751e-14</v>
+        <v>1.740829702612245e-13</v>
       </c>
       <c r="J73" s="24" t="n">
-        <v>3.019806626980426e-14</v>
+        <v>-2.664535259100376e-14</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>1.110223024625157e-14</v>
+        <v>1.154631945610163e-14</v>
       </c>
       <c r="L73" s="24" t="n">
-        <v>-3.419486915845482e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>-1.477706845776083e-13</v>
+        <v>1.932898285872398e-13</v>
       </c>
       <c r="N73" s="24" t="n">
-        <v>2.642330798607873e-14</v>
+        <v>-4.929390229335695e-14</v>
       </c>
       <c r="O73" s="24" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="P73" s="24" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="24" t="n">
-        <v>-3.019806626980426e-14</v>
+        <v>1.332267629550188e-14</v>
       </c>
       <c r="R73" s="24" t="n">
-        <v>-6.616929226765933e-14</v>
+        <v>1.321165399303936e-14</v>
       </c>
       <c r="S73" s="24" t="n">
-        <v>1.119104808822158e-13</v>
+        <v>-2.486899575160351e-14</v>
       </c>
       <c r="T73" s="24" t="n">
-        <v>0</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="U73" s="24" t="n">
-        <v>-3.019806626980426e-14</v>
+        <v>3.996802888650564e-14</v>
       </c>
       <c r="V73" s="24" t="n">
-        <v>-3.042011087472929e-14</v>
+        <v>-4.463096558993129e-14</v>
       </c>
     </row>
     <row r="74">
